--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V91"/>
+  <dimension ref="B1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -940,19 +940,34 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Number of Claims (optional)</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>Section</t>
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1323,7 +1343,7 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1335,457 +1355,345 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="8" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="8" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="10" t="n">
+    <row r="67">
+      <c r="B67" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="10" t="n">
+    <row r="68">
+      <c r="B68" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="10" t="n">
+    <row r="69">
+      <c r="B69" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="2" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
@@ -1798,179 +1706,379 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="8" t="inlineStr">
         <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>01.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>a full-year N in History is an estimate, not an actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="8" t="inlineStr">
+        <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>03.Year basis</t>
         </is>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F80" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="8" t="inlineStr">
+        <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="12" t="inlineStr">
         <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="12" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="8" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2283,17 +2391,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -2355,108 +2464,88 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>— Earthquake —</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>860</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L13" s="18">
-        <f>ROW()</f>
-        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>6450</v>
+        <v>6200</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="L14" s="18">
         <f>ROW()</f>
@@ -2466,17 +2555,17 @@
     <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>915</v>
+        <v>890</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>6700</v>
+        <v>6450</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>8900</v>
+        <v>480</v>
       </c>
       <c r="L15" s="18">
         <f>ROW()</f>
@@ -2486,17 +2575,17 @@
     <row r="16">
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>6980</v>
+        <v>6700</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>620</v>
+        <v>8900</v>
       </c>
       <c r="L16" s="18">
         <f>ROW()</f>
@@ -2506,17 +2595,17 @@
     <row r="17">
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>7250</v>
+        <v>6980</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="L17" s="18">
         <f>ROW()</f>
@@ -2526,17 +2615,17 @@
     <row r="18">
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>2025 9 months</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>745</v>
+        <v>960</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>5430</v>
+        <v>7250</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>410</v>
+        <v>540</v>
       </c>
       <c r="L18" s="18">
         <f>ROW()</f>
@@ -2544,138 +2633,138 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>745</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>5430</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>410</v>
+      </c>
+      <c r="L19" s="18">
+        <f>ROW()</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19" s="19">
-        <f>SUM(C13:C18)</f>
+      <c r="C20" s="19">
+        <f>SUM(C14:C19)</f>
         <v>5310</v>
       </c>
-      <c r="D19" s="19">
-        <f>SUM(D13:D18)</f>
+      <c r="D20" s="19">
+        <f>SUM(D14:D19)</f>
         <v>39010</v>
       </c>
-      <c r="G19" s="19">
-        <f>SUM(G13:G18)</f>
+      <c r="G20" s="19">
+        <f>SUM(G14:G19)</f>
         <v>12150</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>7400</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>2300</v>
-      </c>
-      <c r="L25" s="18">
-        <f>ROW()</f>
-        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1055</v>
+        <v>1020</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>7690</v>
+        <v>7400</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>6800</v>
+        <v>2300</v>
       </c>
       <c r="L26" s="18">
         <f>ROW()</f>
@@ -2685,17 +2774,17 @@
     <row r="27">
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1090</v>
+        <v>1055</v>
       </c>
       <c r="D27" s="17" t="n">
-        <v>7980</v>
+        <v>7690</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>1450</v>
+        <v>6800</v>
       </c>
       <c r="L27" s="18">
         <f>ROW()</f>
@@ -2705,17 +2794,17 @@
     <row r="28">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>8300</v>
+        <v>7980</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>3200</v>
+        <v>1450</v>
       </c>
       <c r="L28" s="18">
         <f>ROW()</f>
@@ -2725,17 +2814,17 @@
     <row r="29">
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="D29" s="17" t="n">
-        <v>8600</v>
+        <v>8300</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>9100</v>
+        <v>3200</v>
       </c>
       <c r="L29" s="18">
         <f>ROW()</f>
@@ -2745,17 +2834,17 @@
     <row r="30">
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>2025 9 months</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>890</v>
+        <v>1150</v>
       </c>
       <c r="D30" s="17" t="n">
-        <v>6440</v>
+        <v>8600</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>5300</v>
+        <v>9100</v>
       </c>
       <c r="L30" s="18">
         <f>ROW()</f>
@@ -2763,31 +2852,51 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>2025 9 months</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>890</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>5300</v>
+      </c>
+      <c r="L31" s="18">
+        <f>ROW()</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C31" s="19">
-        <f>SUM(C25:C30)</f>
+      <c r="C32" s="19">
+        <f>SUM(C26:C31)</f>
         <v>6330</v>
       </c>
-      <c r="D31" s="19">
-        <f>SUM(D25:D30)</f>
+      <c r="D32" s="19">
+        <f>SUM(D26:D31)</f>
         <v>46410</v>
       </c>
-      <c r="G31" s="19">
-        <f>SUM(G25:G30)</f>
+      <c r="G32" s="19">
+        <f>SUM(G26:G31)</f>
         <v>28150</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Info_2 = L</t>
         </is>
@@ -3016,17 +3125,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -3081,81 +3191,67 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>— Earthquake —</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>2025 est</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>7000</v>
-      </c>
-      <c r="K13" s="18">
-        <f>ROW()</f>
-        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>2025 9 months</t>
+          <t>2025 est</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>5430</v>
+        <v>7000</v>
       </c>
       <c r="K14" s="18">
         <f>ROW()</f>
@@ -3165,11 +3261,11 @@
     <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>2025 re-est</t>
+          <t>2025 9 months</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7250</v>
+        <v>5430</v>
       </c>
       <c r="K15" s="18">
         <f>ROW()</f>
@@ -3179,11 +3275,11 @@
     <row r="16">
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025 re-est</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>7900</v>
+        <v>7250</v>
       </c>
       <c r="K16" s="18">
         <f>ROW()</f>
@@ -3191,103 +3287,103 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>7900</v>
+      </c>
+      <c r="K17" s="18">
+        <f>ROW()</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C17" s="19">
-        <f>SUM(C13:C16)</f>
+      <c r="C18" s="19">
+        <f>SUM(C14:C17)</f>
         <v>27580</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>2025 est</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>8300</v>
-      </c>
-      <c r="K23" s="18">
-        <f>ROW()</f>
-        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>2025 9 months</t>
+          <t>2025 est</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>6440</v>
+        <v>8300</v>
       </c>
       <c r="K24" s="18">
         <f>ROW()</f>
@@ -3297,11 +3393,11 @@
     <row r="25">
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>2025 re-est</t>
+          <t>2025 9 months</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>8600</v>
+        <v>6440</v>
       </c>
       <c r="K25" s="18">
         <f>ROW()</f>
@@ -3311,11 +3407,11 @@
     <row r="26">
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025 re-est</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>9250</v>
+        <v>8600</v>
       </c>
       <c r="K26" s="18">
         <f>ROW()</f>
@@ -3323,23 +3419,37 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>9250</v>
+      </c>
+      <c r="K27" s="18">
+        <f>ROW()</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="19">
-        <f>SUM(C23:C26)</f>
+      <c r="C28" s="19">
+        <f>SUM(C24:C27)</f>
         <v>32590</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Info_2 = K</t>
         </is>
@@ -3645,17 +3755,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -3716,131 +3827,142 @@
           <t>Date format = ISO</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>— Earthquake —</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
+          <t>Occurrence year from = Event Date</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>— Earthquake —</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Event no.</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Cat code</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Occurred</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>EV-3100</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Aegean earthquake M6.8</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>44963</v>
-      </c>
-      <c r="J13" s="18">
-        <f>ROW()</f>
-        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EV-3101</t>
+          <t>EV-101</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Central Italy earthquake</t>
+          <t>Aegean earthquake M6.8</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>950</v>
+        <v>400</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>44519</v>
+        <v>44963</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>44963</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>12</v>
       </c>
       <c r="J14" s="18">
         <f>ROW()</f>
@@ -3848,181 +3970,215 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E15" s="19">
-        <f>SUM(E13:E14)</f>
-        <v>8150</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>← selector empty: excluded from extraction, reused as control</t>
-        </is>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>EV-101</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Aegean earthquake M6.8</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>44963</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>44963</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>188</v>
+      </c>
+      <c r="J15" s="18">
+        <f>ROW()</f>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Info_1 = J</t>
-        </is>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>EV-102</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Central Italy earthquake</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>950</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>44519</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>44520</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="J16" s="18">
+        <f>ROW()</f>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E17" s="19">
+        <f>SUM(E14:E16)</f>
+        <v>8150</v>
+      </c>
+      <c r="H17" s="19">
+        <f>SUM(H14:H16)</f>
+        <v>231</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Event no.</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Cat code</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Occurred</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>EV-3100</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Windstorm Eunice</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>5400</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>44610</v>
-      </c>
-      <c r="J21" s="18">
-        <f>ROW()</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>EV-3101</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Windstorm Bettina</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>7600</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>45688</v>
-      </c>
-      <c r="J22" s="18">
-        <f>ROW()</f>
-        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EV-3102</t>
+          <t>EV-201</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Windstorm Kyrill II</t>
+          <t>Windstorm Eunice</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>45635</v>
+        <v>44610</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>44611</v>
       </c>
       <c r="J23" s="18">
         <f>ROW()</f>
@@ -4030,23 +4186,143 @@
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>EV-201</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Eunice</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>44610</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>44611</v>
+      </c>
+      <c r="J24" s="18">
+        <f>ROW()</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>EV-202</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Bettina</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>45656</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>45659</v>
+      </c>
+      <c r="J25" s="18">
+        <f>ROW()</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>EV-202</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Bettina</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>45656</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>45659</v>
+      </c>
+      <c r="J26" s="18">
+        <f>ROW()</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>EV-203</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Kyrill II</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>45635</v>
+      </c>
+      <c r="G27" s="21" t="n">
+        <v>45636</v>
+      </c>
+      <c r="J27" s="18">
+        <f>ROW()</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E24" s="19">
-        <f>SUM(E21:E23)</f>
-        <v>15400</v>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E28" s="19">
+        <f>SUM(E23:E27)</f>
+        <v>14800</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Info_2 = J</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -517,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V96"/>
+  <dimension ref="B1:V97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1206,60 +1207,58 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1271,7 +1270,7 @@
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1283,31 +1282,31 @@
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1319,19 +1318,19 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1343,7 +1342,7 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1355,7 +1354,7 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1367,19 +1366,19 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1391,19 +1390,19 @@
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Date of Loss</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1415,315 +1414,287 @@
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Date format</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="3" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="8" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="10" t="n">
+    <row r="68">
+      <c r="B68" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="10" t="n">
+    <row r="69">
+      <c r="B69" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="10" t="n">
+    <row r="70">
+      <c r="B70" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -1731,9 +1702,9 @@
           <t>=</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
@@ -1751,33 +1722,33 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>01.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
       <c r="F77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -1791,33 +1762,33 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -1826,24 +1797,24 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -1851,7 +1822,7 @@
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
+      <c r="E79" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
@@ -1866,38 +1837,38 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>03.Year basis</t>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -1906,22 +1877,22 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>cat losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
@@ -1931,9 +1902,9 @@
           <t>=</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>04.Year basis</t>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
@@ -1946,139 +1917,179 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="3" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="8" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="12" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="12" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="12" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="12" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="12" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="13" t="inlineStr">
         <is>
           <t>Section_i = &lt;name&gt;</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>which section of the treaty block i belongs to</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="12" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="8" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2117,56 +2128,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2200,22 +2211,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2227,132 +2238,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1240</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>15900</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>14930</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>1310</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>16740</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>10030</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1395</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>17520</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>12660</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>1460</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>18390</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>11700</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1505</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>10250</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>1180</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>7100</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2362,15 +2373,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C12:C17)</f>
         <v>8090</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D12:D17)</f>
         <v>102150</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G12:G17)</f>
         <v>66670</v>
       </c>
@@ -2416,49 +2427,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -2472,7 +2483,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
@@ -2506,22 +2517,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2533,121 +2544,121 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>860</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>6200</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>890</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>6450</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>915</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>6700</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>8900</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>940</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>6980</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>620</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>960</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>7250</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="18" t="n">
         <v>540</v>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="19">
         <f>ROW()</f>
         <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <v>745</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <v>5430</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="18" t="n">
         <v>410</v>
       </c>
-      <c r="L19" s="18">
+      <c r="L19" s="19">
         <f>ROW()</f>
         <v>19</v>
       </c>
@@ -2658,15 +2669,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>SUM(C14:C19)</f>
         <v>5310</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>SUM(D14:D19)</f>
         <v>39010</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <f>SUM(G14:G19)</f>
         <v>12150</v>
       </c>
@@ -2677,7 +2688,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
@@ -2691,7 +2702,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
@@ -2725,22 +2736,22 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2752,121 +2763,121 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>1020</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>7400</v>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="18" t="n">
         <v>2300</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="19">
         <f>ROW()</f>
         <v>26</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>1055</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <v>7690</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="18" t="n">
         <v>6800</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="19">
         <f>ROW()</f>
         <v>27</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="18" t="n">
         <v>1090</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>7980</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="18" t="n">
         <v>1450</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="19">
         <f>ROW()</f>
         <v>28</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="18" t="n">
         <v>1125</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <v>8300</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="18" t="n">
         <v>3200</v>
       </c>
-      <c r="L29" s="18">
+      <c r="L29" s="19">
         <f>ROW()</f>
         <v>29</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="18" t="n">
         <v>1150</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <v>8600</v>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="18" t="n">
         <v>9100</v>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="19">
         <f>ROW()</f>
         <v>30</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="18" t="n">
         <v>890</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <v>6440</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="18" t="n">
         <v>5300</v>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="19">
         <f>ROW()</f>
         <v>31</v>
       </c>
@@ -2877,15 +2888,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <f>SUM(C26:C31)</f>
         <v>6330</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <f>SUM(D26:D31)</f>
         <v>46410</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="20">
         <f>SUM(G26:G31)</f>
         <v>28150</v>
       </c>
@@ -2896,7 +2907,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Info_2 = L</t>
         </is>
@@ -2933,42 +2944,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -2997,17 +3008,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3019,75 +3030,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>18500</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="19">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>20900</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3097,7 +3108,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>SUM(C11:C14)</f>
         <v>73000</v>
       </c>
@@ -3108,7 +3119,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3150,42 +3161,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -3199,7 +3210,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
@@ -3223,17 +3234,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3245,57 +3256,57 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>7000</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>5430</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>7250</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>7900</v>
       </c>
-      <c r="K17" s="18">
+      <c r="K17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
@@ -3306,7 +3317,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C14:C17)</f>
         <v>27580</v>
       </c>
@@ -3317,7 +3328,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3331,7 +3342,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
@@ -3355,17 +3366,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3377,57 +3388,57 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="18" t="n">
         <v>8300</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="19">
         <f>ROW()</f>
         <v>24</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <v>6440</v>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="19">
         <f>ROW()</f>
         <v>25</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>8600</v>
       </c>
-      <c r="K26" s="18">
+      <c r="K26" s="19">
         <f>ROW()</f>
         <v>26</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>9250</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="19">
         <f>ROW()</f>
         <v>27</v>
       </c>
@@ -3438,7 +3449,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>SUM(C24:C27)</f>
         <v>32590</v>
       </c>
@@ -3449,7 +3460,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Info_2 = K</t>
         </is>
@@ -3487,56 +3498,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
@@ -3575,27 +3586,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -3612,7 +3623,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3622,13 +3633,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>1850</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>44269</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3639,7 +3650,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3649,13 +3660,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3666,7 +3677,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -3676,13 +3687,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>2600</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>45431</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3693,7 +3704,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3703,13 +3714,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>1420</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>45699</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3720,7 +3731,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>SUM(E12:E15)</f>
         <v>9270</v>
       </c>
@@ -3731,14 +3742,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3780,56 +3791,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
@@ -3841,7 +3852,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
@@ -3890,42 +3901,42 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Number of Claims</t>
         </is>
@@ -3942,7 +3953,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -3952,19 +3963,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3975,7 +3986,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3985,19 +3996,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>6800</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="18" t="n">
         <v>188</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4008,7 +4019,7 @@
           <t>EV-102</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4018,19 +4029,19 @@
           <t>Central Italy earthquake</t>
         </is>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>950</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="22" t="n">
         <v>44519</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>44520</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -4041,11 +4052,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>SUM(E14:E16)</f>
         <v>8150</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <f>SUM(H14:H16)</f>
         <v>231</v>
       </c>
@@ -4056,7 +4067,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -4070,7 +4081,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
@@ -4114,37 +4125,37 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
@@ -4161,7 +4172,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4171,16 +4182,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="18" t="n">
         <v>1400</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="22" t="n">
         <v>44610</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="22" t="n">
         <v>44611</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="19">
         <f>ROW()</f>
         <v>23</v>
       </c>
@@ -4191,7 +4202,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4201,16 +4212,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="22" t="n">
         <v>44610</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="22" t="n">
         <v>44611</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="19">
         <f>ROW()</f>
         <v>24</v>
       </c>
@@ -4221,7 +4232,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4231,16 +4242,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="22" t="n">
         <v>45656</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="22" t="n">
         <v>45659</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="19">
         <f>ROW()</f>
         <v>25</v>
       </c>
@@ -4251,7 +4262,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -4261,16 +4272,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <v>6600</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="22" t="n">
         <v>45656</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="22" t="n">
         <v>45659</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="19">
         <f>ROW()</f>
         <v>26</v>
       </c>
@@ -4281,7 +4292,7 @@
           <t>EV-203</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4291,16 +4302,16 @@
           <t>Windstorm Kyrill II</t>
         </is>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="18" t="n">
         <v>1800</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="22" t="n">
         <v>45635</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="22" t="n">
         <v>45636</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="19">
         <f>ROW()</f>
         <v>27</v>
       </c>
@@ -4311,7 +4322,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>SUM(E23:E27)</f>
         <v>14800</v>
       </c>
@@ -4322,7 +4333,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Info_2 = J</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V97"/>
+  <dimension ref="B1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2055,41 +2055,53 @@
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Section_i = &lt;name&gt;</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which section of the treaty block i belongs to</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="8" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V98"/>
+  <dimension ref="B1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Greyed rows are provisional sketches, not yet specified.</t>
+          <t>Greyed rows are declared but not yet implemented end to end.</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,27 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Sum Insured</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -1306,7 +1316,7 @@
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band from</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1318,7 +1328,7 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Band to</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1330,31 +1340,31 @@
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1366,7 +1376,7 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1378,408 +1388,352 @@
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="3" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="8" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="8" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="3" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -1788,7 +1742,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -1802,29 +1756,29 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
@@ -1837,38 +1791,38 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -1877,38 +1831,38 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -1922,186 +1876,266 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="3" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="8" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="8" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V100"/>
+  <dimension ref="B1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Band from</t>
+          <t>Band from (optional)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Band to</t>
+          <t>Band to (optional)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1073,10 +1073,25 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1558,262 +1573,206 @@
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Includes fac</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>yes | no</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Layered business</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>included | excluded</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="3" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="8" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -1822,7 +1781,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -1836,29 +1795,29 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
@@ -1871,38 +1830,38 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
@@ -1911,38 +1870,38 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -1956,186 +1915,266 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="8" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="8" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C86" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="3" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="8" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="8" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -14,6 +14,7 @@
     <sheet name="02. EPI Cat" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="03. Large Losses Fire" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="04. Cat Losses" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="05. Risk Profiles" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,12 +55,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
@@ -72,6 +67,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -137,15 +138,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1016,82 +1017,82 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>05. Risk Profiles</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>05 Profile</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Band from (optional)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Band to (optional)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Includes fac</t>
         </is>
       </c>
-      <c r="T11" s="7" t="inlineStr">
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>Layered business</t>
         </is>
       </c>
-      <c r="U11" s="7" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1105,17 +1106,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Datasets</t>
         </is>
@@ -1134,7 +1135,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 03</t>
+          <t>01, 02, 03, 05</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1152,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04</t>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1169,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04</t>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1188,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1204,7 +1205,7 @@
           <t>Actual year</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="8" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -1238,7 +1239,7 @@
           <t>Loss share warning</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="9" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1257,12 +1258,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
@@ -1499,12 +1500,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Permitted values</t>
         </is>
@@ -1662,19 +1663,19 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="11" t="n">
+      <c r="B72" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -1684,7 +1685,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="11" t="n">
+      <c r="B73" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -1694,7 +1695,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="11" t="n">
+      <c r="B74" s="10" t="n">
         <v>3</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -1718,64 +1719,64 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
@@ -1800,22 +1801,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>01.Premium@{N}</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
@@ -1840,22 +1841,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
@@ -1880,22 +1881,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
@@ -1920,22 +1921,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
@@ -1960,22 +1961,22 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>03.Year basis</t>
         </is>
@@ -2000,22 +2001,22 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
@@ -2054,19 +2055,19 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="13" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
@@ -2078,7 +2079,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
@@ -2090,7 +2091,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="13" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
@@ -2102,7 +2103,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="13" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
@@ -2114,7 +2115,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
@@ -2126,7 +2127,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="13" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>Dataset_i = &lt;key&gt;</t>
         </is>
@@ -2138,7 +2139,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="13" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>Section_i = &lt;name&gt;</t>
         </is>
@@ -2150,7 +2151,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="13" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
@@ -2162,7 +2163,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
@@ -2174,7 +2175,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2213,78 +2214,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2448,12 +2449,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -2512,85 +2513,85 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>— Earthquake —</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2749,7 +2750,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -2780,36 +2781,36 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2968,7 +2969,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3029,59 +3030,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3188,7 +3189,7 @@
           <t>Info_1 = K</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3204,7 +3205,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3246,68 +3247,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>— Earthquake —</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
@@ -3397,7 +3398,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3420,26 +3421,26 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
@@ -3529,7 +3530,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3583,83 +3584,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -3811,7 +3812,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3834,7 +3835,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3876,105 +3877,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>— Earthquake —</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
@@ -4132,7 +4133,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4159,46 +4160,46 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>— Windstorm —</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -4402,7 +4403,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4421,6 +4422,803 @@
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Info_2 = J</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles — Fire, EQ and Windstorm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Layered business = excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>— Fire —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Section_1 = Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>As at_1 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0 – 1 000</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>620</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>310000</v>
+      </c>
+      <c r="J12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1 001 – 5 000</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>480</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="J13" s="19">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>5 001 – 10 000</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>5001</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="J14" s="19">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 25 000</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>2010000</v>
+      </c>
+      <c r="J15" s="19">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 25 000</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="J16" s="19">
+        <f>ROW()</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E17" s="20">
+        <f>SUM(E12:E16)</f>
+        <v>20150</v>
+      </c>
+      <c r="F17" s="20">
+        <f>SUM(F12:F16)</f>
+        <v>1505</v>
+      </c>
+      <c r="G17" s="20">
+        <f>SUM(G12:G16)</f>
+        <v>6630000</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>— Earthquake —</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Section_2 = Earthquake</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>As at_2 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Header_2</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>0 – 2 500</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>380</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J24" s="19">
+        <f>ROW()</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2 501 – 10 000</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>310</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>690000</v>
+      </c>
+      <c r="J25" s="19">
+        <f>ROW()</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 50 000</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>190</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>1420000</v>
+      </c>
+      <c r="J26" s="19">
+        <f>ROW()</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 50 000</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>980000</v>
+      </c>
+      <c r="J27" s="19">
+        <f>ROW()</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E28" s="20">
+        <f>SUM(E24:E27)</f>
+        <v>7580</v>
+      </c>
+      <c r="F28" s="20">
+        <f>SUM(F24:F27)</f>
+        <v>960</v>
+      </c>
+      <c r="G28" s="20">
+        <f>SUM(G24:G27)</f>
+        <v>3330000</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Info_2 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>— Windstorm —</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Section_3 = Windstorm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>As at_3 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Header_3</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>0 – 2 500</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>450</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>290000</v>
+      </c>
+      <c r="J35" s="19">
+        <f>ROW()</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2 501 – 10 000</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>370</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>810000</v>
+      </c>
+      <c r="J36" s="19">
+        <f>ROW()</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 50 000</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>3180</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>240</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="J37" s="19">
+        <f>ROW()</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 50 000</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="J38" s="19">
+        <f>ROW()</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E39" s="20">
+        <f>SUM(E35:E38)</f>
+        <v>9060</v>
+      </c>
+      <c r="F39" s="20">
+        <f>SUM(F35:F38)</f>
+        <v>1150</v>
+      </c>
+      <c r="G39" s="20">
+        <f>SUM(G35:G38)</f>
+        <v>3900000</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Info_3 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>One profile per line of business. The top band is open at the top, so its upper bound is absent rather than zero.</t>
         </is>
       </c>
     </row>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Band (optional)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +139,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -519,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V102"/>
+  <dimension ref="B1:V119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1101,1081 +1102,1381 @@
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>⟦SECTIONS⟧</t>
+          <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Holds</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>History</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05</t>
+          <t>Premium and loss history per section</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>EPI Projections</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05</t>
+          <t>Estimated premium income, N and N+1</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Windstorm</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Large Losses</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05</t>
+          <t>Individual large claims, per-risk sections</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Cat Losses</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Catastrophe events, cat sections</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Risk Profiles</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Banded exposure — the per-risk rating basis</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>EQ Aggs</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>⟦GLOBAL⟧</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Wind Aggs</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Splits</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>axes settled, measures open</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>2025</v>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Rate Development</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Rate change history — optional</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Fire + Nat Cat</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Triangles</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Loss development triangles</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>0.2</v>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Collected step-2 blocks — written, never read</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+          <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>⟦TYPES⟧</t>
+          <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Datasets</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 03, 05</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Windstorm</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Band from</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Band to</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Number of Risks</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Fire + Nat Cat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Loss amount</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Number of Claims</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Date of Loss</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>A field name carries one type across the whole workbook.</t>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>yes | no</t>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>included | excluded</t>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>100% | ceded only</t>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Event Date | Event End Date</t>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>UW | Occurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>included | excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="3" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="7" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="10" t="n">
+    <row r="89">
+      <c r="B89" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="10" t="n">
+    <row r="90">
+      <c r="B90" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="10" t="n">
+    <row r="91">
+      <c r="B91" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="2" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="3" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="7" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="7" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C80" s="11" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F97" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="7" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N}</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="4" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="7" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C99" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F99" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="G99" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="7" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E83" s="11" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F100" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H100" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C101" s="12" t="inlineStr">
         <is>
           <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F101" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>cat losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C85" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>03.Year basis</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>04.Year basis</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>history and cat losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Marker</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Dataset_i = &lt;key&gt;</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>Section_i = &lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>which section of the treaty block i belongs to</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>Header_i</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Header_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this column is block i's extraction column</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Dataset_i = &lt;key&gt;</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>the same, declared as a hypothesis — raises a query</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2214,78 +2515,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2297,22 +2598,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2324,132 +2625,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1240</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>15900</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>14930</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1310</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>16740</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>10030</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1395</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>17520</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>12660</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1460</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>18390</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>11700</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1505</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>10250</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>1180</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>7100</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2459,15 +2760,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>8090</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>102150</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>66670</v>
       </c>
@@ -2513,49 +2814,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
@@ -2569,29 +2870,29 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2603,22 +2904,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2630,121 +2931,121 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>860</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>6200</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>6450</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>915</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>6700</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>8900</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>940</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>6980</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="19" t="n">
         <v>960</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>540</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="20">
         <f>ROW()</f>
         <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="19" t="n">
         <v>745</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>410</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="20">
         <f>ROW()</f>
         <v>19</v>
       </c>
@@ -2755,15 +3056,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <f>SUM(C14:C19)</f>
         <v>5310</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <f>SUM(D14:D19)</f>
         <v>39010</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="21">
         <f>SUM(G14:G19)</f>
         <v>12150</v>
       </c>
@@ -2774,7 +3075,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
@@ -2788,29 +3089,29 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -2822,22 +3123,22 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2849,121 +3150,121 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>1020</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>7400</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="19" t="n">
         <v>2300</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="20">
         <f>ROW()</f>
         <v>26</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>1055</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="19" t="n">
         <v>7690</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="20">
         <f>ROW()</f>
         <v>27</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="19" t="n">
         <v>1090</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="19" t="n">
         <v>7980</v>
       </c>
-      <c r="G28" s="18" t="n">
+      <c r="G28" s="19" t="n">
         <v>1450</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="20">
         <f>ROW()</f>
         <v>28</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="19" t="n">
         <v>1125</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="19" t="n">
         <v>3200</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="20">
         <f>ROW()</f>
         <v>29</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
+      <c r="C30" s="19" t="n">
         <v>1150</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="19" t="n">
         <v>9100</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="20">
         <f>ROW()</f>
         <v>30</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n">
+      <c r="C31" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="19" t="n">
         <v>5300</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="20">
         <f>ROW()</f>
         <v>31</v>
       </c>
@@ -2974,15 +3275,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <f>SUM(C26:C31)</f>
         <v>6330</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <f>SUM(D26:D31)</f>
         <v>46410</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <f>SUM(G26:G31)</f>
         <v>28150</v>
       </c>
@@ -2993,7 +3294,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Info_2 = L</t>
         </is>
@@ -3030,59 +3331,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3094,17 +3395,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3116,75 +3417,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>18500</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>20900</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3194,7 +3495,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>73000</v>
       </c>
@@ -3205,7 +3506,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3247,42 +3548,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -3296,19 +3597,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
@@ -3320,17 +3621,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3342,57 +3643,57 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>7000</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>7900</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
@@ -3403,7 +3704,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C14:C17)</f>
         <v>27580</v>
       </c>
@@ -3414,7 +3715,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3428,19 +3729,19 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
@@ -3452,17 +3753,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3474,57 +3775,57 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <f>ROW()</f>
         <v>24</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="20">
         <f>ROW()</f>
         <v>25</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <f>ROW()</f>
         <v>26</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>9250</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="20">
         <f>ROW()</f>
         <v>27</v>
       </c>
@@ -3535,7 +3836,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="21">
         <f>SUM(C24:C27)</f>
         <v>32590</v>
       </c>
@@ -3546,7 +3847,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Info_2 = K</t>
         </is>
@@ -3584,83 +3885,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -3672,27 +3973,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -3709,7 +4010,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -3719,13 +4020,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1850</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44269</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3736,7 +4037,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -3746,13 +4047,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3763,7 +4064,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -3773,13 +4074,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>2600</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>45431</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3790,7 +4091,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3800,13 +4101,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1420</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>45699</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3817,7 +4118,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>SUM(E12:E15)</f>
         <v>9270</v>
       </c>
@@ -3828,14 +4129,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3877,56 +4178,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
@@ -3938,44 +4239,44 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
@@ -3987,42 +4288,42 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>Number of Claims</t>
         </is>
@@ -4039,7 +4340,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4049,19 +4350,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4072,7 +4373,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -4082,19 +4383,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="19" t="n">
         <v>188</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4105,7 +4406,7 @@
           <t>EV-102</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4115,19 +4416,19 @@
           <t>Central Italy earthquake</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>950</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>44519</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>44520</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -4138,11 +4439,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>SUM(E14:E16)</f>
         <v>8150</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="21">
         <f>SUM(H14:H16)</f>
         <v>231</v>
       </c>
@@ -4153,7 +4454,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -4167,39 +4468,39 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -4211,37 +4512,37 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
@@ -4258,7 +4559,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4268,16 +4569,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="19" t="n">
         <v>1400</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="20">
         <f>ROW()</f>
         <v>23</v>
       </c>
@@ -4288,7 +4589,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4298,16 +4599,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G24" s="22" t="n">
+      <c r="G24" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <f>ROW()</f>
         <v>24</v>
       </c>
@@ -4318,7 +4619,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4328,16 +4629,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F25" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G25" s="22" t="n">
+      <c r="G25" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="20">
         <f>ROW()</f>
         <v>25</v>
       </c>
@@ -4348,7 +4649,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -4358,16 +4659,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="19" t="n">
         <v>6600</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="20">
         <f>ROW()</f>
         <v>26</v>
       </c>
@@ -4378,7 +4679,7 @@
           <t>EV-203</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4388,16 +4689,16 @@
           <t>Windstorm Kyrill II</t>
         </is>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="F27" s="22" t="n">
+      <c r="F27" s="23" t="n">
         <v>45635</v>
       </c>
-      <c r="G27" s="22" t="n">
+      <c r="G27" s="23" t="n">
         <v>45636</v>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="20">
         <f>ROW()</f>
         <v>27</v>
       </c>
@@ -4408,7 +4709,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="21">
         <f>SUM(E23:E27)</f>
         <v>14800</v>
       </c>
@@ -4419,7 +4720,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Info_2 = J</t>
         </is>
@@ -4458,42 +4759,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Exposure basis = Sum Insured</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Includes fac = yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Layered business = excluded</t>
         </is>
@@ -4507,44 +4808,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Fire</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at_1 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -4556,37 +4857,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -4603,22 +4904,22 @@
           <t>0 – 1 000</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>2150</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>310000</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -4629,22 +4930,22 @@
           <t>1 001 – 5 000</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1001</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>4900</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>1290000</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -4655,22 +4956,22 @@
           <t>5 001 – 10 000</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>5300</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>260</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1880000</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4681,22 +4982,22 @@
           <t>10 001 – 25 000</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>25000</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>4700</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>118</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>2010000</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4707,19 +5008,19 @@
           <t>&gt; 25 000</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>25000</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>3100</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>1140000</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -4730,15 +5031,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>SUM(E12:E16)</f>
         <v>20150</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <f>SUM(F12:F16)</f>
         <v>1505</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="21">
         <f>SUM(G12:G16)</f>
         <v>6630000</v>
       </c>
@@ -4749,7 +5050,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -4763,44 +5064,44 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Section_2 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>As at_2 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -4812,37 +5113,37 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Header_2</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -4859,22 +5160,22 @@
           <t>0 – 2 500</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>2500</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="19" t="n">
         <v>1050</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="19" t="n">
         <v>380</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="19" t="n">
         <v>240000</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <f>ROW()</f>
         <v>24</v>
       </c>
@@ -4885,22 +5186,22 @@
           <t>2 501 – 10 000</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="19" t="n">
         <v>2501</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="19" t="n">
         <v>2300</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="19" t="n">
         <v>310</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="19" t="n">
         <v>690000</v>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="20">
         <f>ROW()</f>
         <v>25</v>
       </c>
@@ -4911,22 +5212,22 @@
           <t>10 001 – 50 000</t>
         </is>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="19" t="n">
         <v>2750</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="19" t="n">
         <v>190</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="19" t="n">
         <v>1420000</v>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="20">
         <f>ROW()</f>
         <v>26</v>
       </c>
@@ -4937,19 +5238,19 @@
           <t>&gt; 50 000</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="19" t="n">
         <v>1480</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="19" t="n">
         <v>80</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="19" t="n">
         <v>980000</v>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="20">
         <f>ROW()</f>
         <v>27</v>
       </c>
@@ -4960,15 +5261,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="21">
         <f>SUM(E24:E27)</f>
         <v>7580</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="21">
         <f>SUM(F24:F27)</f>
         <v>960</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="21">
         <f>SUM(G24:G27)</f>
         <v>3330000</v>
       </c>
@@ -4979,7 +5280,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Info_2 = J</t>
         </is>
@@ -4993,44 +5294,44 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Section_3 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>As at_3 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -5042,37 +5343,37 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Header_3</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -5089,22 +5390,22 @@
           <t>0 – 2 500</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n">
+      <c r="C35" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="19" t="n">
         <v>2500</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="19" t="n">
         <v>1320</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="19" t="n">
         <v>450</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G35" s="19" t="n">
         <v>290000</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="20">
         <f>ROW()</f>
         <v>35</v>
       </c>
@@ -5115,22 +5416,22 @@
           <t>2 501 – 10 000</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="19" t="n">
         <v>2501</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="19" t="n">
         <v>2650</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="19" t="n">
         <v>370</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="19" t="n">
         <v>810000</v>
       </c>
-      <c r="J36" s="19">
+      <c r="J36" s="20">
         <f>ROW()</f>
         <v>36</v>
       </c>
@@ -5141,22 +5442,22 @@
           <t>10 001 – 50 000</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C37" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="19" t="n">
         <v>3180</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="19" t="n">
         <v>240</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="19" t="n">
         <v>1680000</v>
       </c>
-      <c r="J37" s="19">
+      <c r="J37" s="20">
         <f>ROW()</f>
         <v>37</v>
       </c>
@@ -5167,19 +5468,19 @@
           <t>&gt; 50 000</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
+      <c r="C38" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="19" t="n">
         <v>1910</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G38" s="18" t="n">
+      <c r="G38" s="19" t="n">
         <v>1120000</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="20">
         <f>ROW()</f>
         <v>38</v>
       </c>
@@ -5190,15 +5491,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="21">
         <f>SUM(E35:E38)</f>
         <v>9060</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="21">
         <f>SUM(F35:F38)</f>
         <v>1150</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="21">
         <f>SUM(G35:G38)</f>
         <v>3900000</v>
       </c>
@@ -5209,7 +5510,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Info_3 = J</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -1295,12 +1295,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>axes settled, measures open</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V119"/>
+  <dimension ref="B1:V121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2005,156 +2005,96 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="B92" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>at inception</t>
+        </is>
+      </c>
+    </row>
     <row r="93">
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>at expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="3" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -2163,7 +2103,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
@@ -2177,29 +2117,29 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
@@ -2212,38 +2152,38 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
@@ -2252,38 +2192,38 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
@@ -2297,186 +2237,266 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E103" s="12" t="inlineStr">
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F105" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="2" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="3" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="7" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="B119" s="7" t="inlineStr">
+    <row r="121">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireCat_v1.xlsx
+++ b/Intake_FireCat_v1.xlsx
@@ -1317,12 +1317,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
